--- a/DevKit_回归测试报告.xlsx
+++ b/DevKit_回归测试报告.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="609">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="610">
   <si>
     <t>DevKit 回归测试 · 结论汇总</t>
   </si>
@@ -395,10 +395,10 @@
     <t>补齐串口功能实现，或在功能就绪前先从菜单中隐藏该入口，避免误导用户</t>
   </si>
   <si>
-    <t>暂不处理</t>
-  </si>
-  <si>
     <t>SerialPortView.xaml 仍为 &lt;Grid /&gt; 空布局，SerialPortViewModel 仍为空壳；菜单已注册但点击后为纯空白窗口，无「开发中」提示。属未上线功能占位，建议隐藏入口或置灰。</t>
+  </si>
+  <si>
+    <t>预留功能，暂不处理</t>
   </si>
   <si>
     <t>BUG-006</t>
@@ -762,6 +762,9 @@
   </si>
   <si>
     <t>AddRecentlyColor 本身已做 ToUpperInvariant + OrdinalIgnoreCase 去重(:367-372)，但两条入库路径格式不统一：输入框路径 AddRecentlyColor(value) 存原始值(如 ff0000)，色块路径 AddRecentlyColor(CurrentColorHex) 存带 # 的规范化值，同一颜色仍可能以两种格式重复入库。</t>
+  </si>
+  <si>
+    <t>HEX 输入框输入不接受回车事件，问题不存在</t>
   </si>
   <si>
     <t>BUG-018</t>
@@ -1944,7 +1947,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="40">
+  <fonts count="39">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2017,14 +2020,6 @@
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF00B050"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -2249,7 +2244,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="46">
+  <fills count="44">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2306,19 +2301,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.15"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFF6D3F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2645,85 +2628,91 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2732,10 +2721,10 @@
     <xf numFmtId="0" fontId="38" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2744,10 +2733,10 @@
     <xf numFmtId="0" fontId="38" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2756,10 +2745,10 @@
     <xf numFmtId="0" fontId="38" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2768,10 +2757,10 @@
     <xf numFmtId="0" fontId="38" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2780,17 +2769,11 @@
     <xf numFmtId="0" fontId="38" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2838,27 +2821,24 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2870,22 +2850,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2903,13 +2883,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3281,22 +3261,22 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:13">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="22" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="22" t="s">
         <v>3</v>
       </c>
     </row>
@@ -3322,175 +3302,175 @@
       <c r="H6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="I6" s="24"/>
-      <c r="J6" s="24"/>
-      <c r="K6" s="24"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="23"/>
+      <c r="K6" s="23"/>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:13">
-      <c r="A7" s="25" t="s">
+      <c r="A7" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="26">
+      <c r="B7" s="25">
         <v>7</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="26">
         <v>0.233333333333333</v>
       </c>
-      <c r="D7" s="28" t="s">
+      <c r="D7" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="28" t="s">
+      <c r="E7" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="26" t="s">
+      <c r="F7" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="H7" s="29" t="s">
+      <c r="H7" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="30" t="s">
+      <c r="I7" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="30"/>
-      <c r="K7" s="30" t="s">
+      <c r="J7" s="29"/>
+      <c r="K7" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="L7" s="30"/>
-      <c r="M7" s="30"/>
+      <c r="L7" s="29"/>
+      <c r="M7" s="29"/>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:13">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="26">
+      <c r="B8" s="25">
         <v>11</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="26">
         <v>0.366666666666667</v>
       </c>
-      <c r="D8" s="28" t="s">
+      <c r="D8" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="28" t="s">
+      <c r="E8" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="26" t="s">
+      <c r="F8" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="H8" s="29" t="s">
+      <c r="H8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="I8" s="30" t="s">
+      <c r="I8" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="J8" s="30"/>
-      <c r="K8" s="30" t="s">
+      <c r="J8" s="29"/>
+      <c r="K8" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="L8" s="30"/>
-      <c r="M8" s="30"/>
+      <c r="L8" s="29"/>
+      <c r="M8" s="29"/>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:13">
-      <c r="A9" s="32" t="s">
+      <c r="A9" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="26">
+      <c r="B9" s="25">
         <v>3</v>
       </c>
-      <c r="C9" s="27">
+      <c r="C9" s="26">
         <v>0.1</v>
       </c>
-      <c r="D9" s="28" t="s">
+      <c r="D9" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="28" t="s">
+      <c r="E9" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="26" t="s">
+      <c r="F9" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="H9" s="29" t="s">
+      <c r="H9" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="I9" s="30" t="s">
+      <c r="I9" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="J9" s="30"/>
-      <c r="K9" s="30" t="s">
+      <c r="J9" s="29"/>
+      <c r="K9" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="L9" s="30"/>
-      <c r="M9" s="30"/>
+      <c r="L9" s="29"/>
+      <c r="M9" s="29"/>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:13">
-      <c r="A10" s="33" t="s">
+      <c r="A10" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="26">
+      <c r="B10" s="25">
         <v>4</v>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="26">
         <v>0.133333333333333</v>
       </c>
-      <c r="D10" s="28" t="s">
+      <c r="D10" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="28" t="s">
+      <c r="E10" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="26" t="s">
+      <c r="F10" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="H10" s="29" t="s">
+      <c r="H10" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I10" s="30" t="s">
+      <c r="I10" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="J10" s="30"/>
-      <c r="K10" s="30" t="s">
+      <c r="J10" s="29"/>
+      <c r="K10" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="L10" s="30"/>
-      <c r="M10" s="30"/>
+      <c r="L10" s="29"/>
+      <c r="M10" s="29"/>
     </row>
     <row r="11" spans="1:13">
-      <c r="A11" s="34" t="s">
+      <c r="A11" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="26">
+      <c r="B11" s="25">
         <v>5</v>
       </c>
-      <c r="C11" s="27">
+      <c r="C11" s="26">
         <v>0.166666666666667</v>
       </c>
-      <c r="D11" s="28" t="s">
+      <c r="D11" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="E11" s="28" t="s">
+      <c r="E11" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="26" t="s">
+      <c r="F11" s="25" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="12" ht="27" spans="1:13">
-      <c r="A12" s="35" t="s">
+      <c r="A12" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="36">
+      <c r="B12" s="35">
         <v>30</v>
       </c>
-      <c r="C12" s="37">
+      <c r="C12" s="36">
         <v>1</v>
       </c>
-      <c r="D12" s="35" t="s">
+      <c r="D12" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="E12" s="35" t="s">
+      <c r="E12" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="F12" s="36" t="s">
+      <c r="F12" s="35" t="s">
         <v>14</v>
       </c>
     </row>
@@ -3498,37 +3478,37 @@
       <c r="H13" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I13" s="24"/>
+      <c r="I13" s="23"/>
     </row>
     <row r="14" spans="1:13">
-      <c r="H14" s="38" t="s">
+      <c r="H14" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="I14" s="39">
+      <c r="I14" s="38">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:13">
-      <c r="H15" s="40" t="s">
+      <c r="H15" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="I15" s="39">
+      <c r="I15" s="38">
         <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:13">
-      <c r="H16" s="41" t="s">
+      <c r="H16" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="I16" s="39">
+      <c r="I16" s="38">
         <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="H17" s="42" t="s">
+      <c r="H17" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="I17" s="39">
+      <c r="I17" s="38">
         <v>6</v>
       </c>
     </row>
@@ -3536,40 +3516,40 @@
       <c r="A18" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="H18" s="43" t="s">
+      <c r="H18" s="42" t="s">
         <v>48</v>
       </c>
-      <c r="I18" s="43">
+      <c r="I18" s="42">
         <v>16</v>
       </c>
     </row>
     <row r="19" ht="26" customHeight="1" spans="1:9">
-      <c r="A19" s="44" t="s">
+      <c r="A19" s="43" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="20" ht="26" customHeight="1" spans="1:9">
-      <c r="A20" s="44" t="s">
+      <c r="A20" s="43" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="21" ht="26" customHeight="1" spans="1:9">
-      <c r="A21" s="44" t="s">
+      <c r="A21" s="43" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1" spans="1:9">
-      <c r="A22" s="44" t="s">
+      <c r="A22" s="43" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="23" ht="26" customHeight="1" spans="1:9">
-      <c r="A23" s="44" t="s">
+      <c r="A23" s="43" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="24" ht="26" customHeight="1" spans="1:9">
-      <c r="A24" s="44" t="s">
+      <c r="A24" s="43" t="s">
         <v>54</v>
       </c>
     </row>
@@ -3605,7 +3585,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="16" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
     <col min="4" max="4" width="40" customWidth="1"/>
     <col min="5" max="5" width="24" customWidth="1"/>
@@ -3617,12 +3597,12 @@
     <col min="12" max="12" width="56" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:12">
+    <row r="1" ht="28" customHeight="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1" spans="1:12">
+    <row r="3" ht="24" customHeight="1" spans="1:13">
       <c r="A3" s="2" t="s">
         <v>56</v>
       </c>
@@ -3660,7 +3640,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="4" ht="92" hidden="1" customHeight="1" spans="1:12">
+    <row r="4" ht="92" customHeight="1" spans="1:13">
       <c r="A4" s="3" t="s">
         <v>67</v>
       </c>
@@ -3698,7 +3678,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="5" ht="92" hidden="1" customHeight="1" spans="1:12">
+    <row r="5" ht="92" customHeight="1" spans="1:13">
       <c r="A5" s="3" t="s">
         <v>77</v>
       </c>
@@ -3736,7 +3716,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="6" ht="92" hidden="1" customHeight="1" spans="1:12">
+    <row r="6" ht="92" customHeight="1" spans="1:13">
       <c r="A6" s="3" t="s">
         <v>87</v>
       </c>
@@ -3774,7 +3754,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="7" ht="92" hidden="1" customHeight="1" spans="1:12">
+    <row r="7" ht="92" customHeight="1" spans="1:13">
       <c r="A7" s="3" t="s">
         <v>96</v>
       </c>
@@ -3812,7 +3792,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="8" ht="92" customHeight="1" spans="1:12">
+    <row r="8" ht="92" customHeight="1" spans="1:13">
       <c r="A8" s="3" t="s">
         <v>105</v>
       </c>
@@ -3843,14 +3823,17 @@
       <c r="J8" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="K8" s="17" t="s">
+      <c r="K8" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="L8" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="L8" s="4" t="s">
+      <c r="M8" s="17" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="9" ht="92" hidden="1" customHeight="1" spans="1:12">
+    <row r="9" ht="92" customHeight="1" spans="1:13">
       <c r="A9" s="3" t="s">
         <v>116</v>
       </c>
@@ -3888,7 +3871,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="10" ht="92" hidden="1" customHeight="1" spans="1:12">
+    <row r="10" ht="92" hidden="1" customHeight="1" spans="1:13">
       <c r="A10" s="3" t="s">
         <v>125</v>
       </c>
@@ -3926,7 +3909,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="11" ht="92" hidden="1" customHeight="1" spans="1:12">
+    <row r="11" ht="92" customHeight="1" spans="1:13">
       <c r="A11" s="3" t="s">
         <v>134</v>
       </c>
@@ -3964,7 +3947,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="12" ht="92" hidden="1" customHeight="1" spans="1:12">
+    <row r="12" ht="92" hidden="1" customHeight="1" spans="1:13">
       <c r="A12" s="3" t="s">
         <v>144</v>
       </c>
@@ -4002,7 +3985,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="13" ht="92" hidden="1" customHeight="1" spans="1:12">
+    <row r="13" ht="92" customHeight="1" spans="1:13">
       <c r="A13" s="3" t="s">
         <v>152</v>
       </c>
@@ -4040,7 +4023,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="14" ht="92" customHeight="1" spans="1:12">
+    <row r="14" ht="92" customHeight="1" spans="1:13">
       <c r="A14" s="3" t="s">
         <v>161</v>
       </c>
@@ -4071,21 +4054,21 @@
       <c r="J14" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="K14" s="19" t="s">
+      <c r="K14" s="6" t="s">
         <v>11</v>
       </c>
       <c r="L14" s="4" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="15" ht="92" hidden="1" customHeight="1" spans="1:12">
+    <row r="15" ht="92" hidden="1" customHeight="1" spans="1:13">
       <c r="A15" s="3" t="s">
         <v>170</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="19" t="s">
         <v>47</v>
       </c>
       <c r="D15" s="5" t="s">
@@ -4109,14 +4092,14 @@
       <c r="J15" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="K15" s="21" t="s">
+      <c r="K15" s="20" t="s">
         <v>31</v>
       </c>
       <c r="L15" s="4" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="16" ht="92" customHeight="1" spans="1:12">
+    <row r="16" ht="92" customHeight="1" spans="1:13">
       <c r="A16" s="3" t="s">
         <v>180</v>
       </c>
@@ -4154,14 +4137,14 @@
         <v>188</v>
       </c>
     </row>
-    <row r="17" ht="92" hidden="1" customHeight="1" spans="1:12">
+    <row r="17" ht="92" hidden="1" customHeight="1" spans="1:13">
       <c r="A17" s="3" t="s">
         <v>189</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="C17" s="20" t="s">
+      <c r="C17" s="19" t="s">
         <v>47</v>
       </c>
       <c r="D17" s="5" t="s">
@@ -4185,14 +4168,14 @@
       <c r="J17" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="K17" s="21" t="s">
+      <c r="K17" s="20" t="s">
         <v>31</v>
       </c>
       <c r="L17" s="4" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="18" ht="92" hidden="1" customHeight="1" spans="1:12">
+    <row r="18" ht="92" hidden="1" customHeight="1" spans="1:13">
       <c r="A18" s="3" t="s">
         <v>199</v>
       </c>
@@ -4230,7 +4213,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="19" ht="92" hidden="1" customHeight="1" spans="1:12">
+    <row r="19" ht="92" hidden="1" customHeight="1" spans="1:13">
       <c r="A19" s="3" t="s">
         <v>208</v>
       </c>
@@ -4261,21 +4244,21 @@
       <c r="J19" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="K19" s="21" t="s">
+      <c r="K19" s="20" t="s">
         <v>31</v>
       </c>
       <c r="L19" s="4" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="20" ht="92" customHeight="1" spans="1:12">
+    <row r="20" ht="92" customHeight="1" spans="1:13">
       <c r="A20" s="3" t="s">
         <v>218</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="C20" s="20" t="s">
+      <c r="C20" s="19" t="s">
         <v>47</v>
       </c>
       <c r="D20" s="5" t="s">
@@ -4305,86 +4288,92 @@
       <c r="L20" s="4" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="21" ht="92" hidden="1" customHeight="1" spans="1:12">
+      <c r="M20" s="17" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="21" ht="92" hidden="1" customHeight="1" spans="1:13">
       <c r="A21" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C21" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="K21" s="21" t="s">
+        <v>237</v>
+      </c>
+      <c r="K21" s="20" t="s">
         <v>31</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="22" ht="92" customHeight="1" spans="1:12">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="22" ht="92" customHeight="1" spans="1:13">
       <c r="A22" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="C22" s="20" t="s">
+        <v>240</v>
+      </c>
+      <c r="C22" s="19" t="s">
         <v>47</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>108</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K22" s="8" t="s">
         <v>18</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="23" ht="92" customHeight="1" spans="1:12">
+        <v>247</v>
+      </c>
+      <c r="M22" s="17" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="23" ht="92" customHeight="1" spans="1:13">
       <c r="A23" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>97</v>
@@ -4393,74 +4382,74 @@
         <v>46</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K23" s="8" t="s">
         <v>18</v>
       </c>
       <c r="L23" s="4" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="24" ht="92" customHeight="1" spans="1:12">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="24" ht="92" customHeight="1" spans="1:13">
       <c r="A24" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C24" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K24" s="8" t="s">
         <v>18</v>
       </c>
       <c r="L24" s="4" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="25" ht="92" customHeight="1" spans="1:12">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="25" ht="92" customHeight="1" spans="1:13">
       <c r="A25" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>78</v>
@@ -4469,335 +4458,335 @@
         <v>45</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K25" s="8" t="s">
         <v>18</v>
       </c>
       <c r="L25" s="4" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="26" ht="92" customHeight="1" spans="1:12">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="26" ht="92" customHeight="1" spans="1:13">
       <c r="A26" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="C26" s="20" t="s">
+        <v>258</v>
+      </c>
+      <c r="C26" s="19" t="s">
         <v>47</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K26" s="8" t="s">
         <v>18</v>
       </c>
       <c r="L26" s="4" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="27" ht="92" customHeight="1" spans="1:12">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="27" ht="92" customHeight="1" spans="1:13">
       <c r="A27" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="C27" s="20" t="s">
+        <v>286</v>
+      </c>
+      <c r="C27" s="19" t="s">
         <v>47</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="K27" s="8" t="s">
-        <v>18</v>
+        <v>293</v>
+      </c>
+      <c r="K27" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="L27" s="4" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="28" ht="92" customHeight="1" spans="1:12">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="28" ht="92" customHeight="1" spans="1:13">
       <c r="A28" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C28" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K28" s="8" t="s">
         <v>18</v>
       </c>
       <c r="L28" s="4" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="29" ht="92" customHeight="1" spans="1:12">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="29" ht="92" customHeight="1" spans="1:13">
       <c r="A29" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C29" s="18" t="s">
         <v>45</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K29" s="9" t="s">
         <v>37</v>
       </c>
       <c r="L29" s="4" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="30" ht="92" customHeight="1" spans="1:12">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="30" ht="92" customHeight="1" spans="1:13">
       <c r="A30" s="3" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C30" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K30" s="9" t="s">
         <v>37</v>
       </c>
       <c r="L30" s="4" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="31" ht="92" customHeight="1" spans="1:12">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="31" ht="92" customHeight="1" spans="1:13">
       <c r="A31" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="C31" s="20" t="s">
+        <v>324</v>
+      </c>
+      <c r="C31" s="19" t="s">
         <v>47</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K31" s="9" t="s">
         <v>37</v>
       </c>
       <c r="L31" s="4" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="32" ht="92" customHeight="1" spans="1:12">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="32" ht="92" customHeight="1" spans="1:13">
       <c r="A32" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C32" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K32" s="9" t="s">
         <v>37</v>
       </c>
       <c r="L32" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="33" ht="92" customHeight="1" spans="1:12">
       <c r="A33" s="3" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="C33" s="20" t="s">
+        <v>342</v>
+      </c>
+      <c r="C33" s="19" t="s">
         <v>47</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K33" s="9" t="s">
         <v>37</v>
       </c>
       <c r="L33" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -4805,6 +4794,7 @@
     <filterColumn colId="10">
       <filters>
         <filter val="仍存在"/>
+        <filter val="已修复"/>
         <filter val="新增"/>
       </filters>
     </filterColumn>
@@ -4836,18 +4826,18 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:8">
       <c r="A3" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>57</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>60</v>
@@ -4856,36 +4846,36 @@
         <v>62</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:8">
       <c r="A4" s="3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>68</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>67</v>
@@ -4893,25 +4883,25 @@
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:8">
       <c r="A5" s="3" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>68</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>67</v>
@@ -4919,25 +4909,25 @@
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:8">
       <c r="A6" s="3" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>68</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>152</v>
@@ -4945,129 +4935,129 @@
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:8">
       <c r="A7" s="3" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>68</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:8">
       <c r="A8" s="3" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>68</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:8">
       <c r="A9" s="3" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>68</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:8">
       <c r="A10" s="3" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>135</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1" spans="1:8">
       <c r="A11" s="3" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>135</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>134</v>
@@ -5075,51 +5065,51 @@
     </row>
     <row r="12" ht="34" customHeight="1" spans="1:8">
       <c r="A12" s="3" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>135</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1" spans="1:8">
       <c r="A13" s="3" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>78</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>77</v>
@@ -5127,103 +5117,103 @@
     </row>
     <row r="14" ht="34" customHeight="1" spans="1:8">
       <c r="A14" s="3" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>78</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1" spans="1:8">
       <c r="A15" s="3" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>78</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="16" ht="34" customHeight="1" spans="1:8">
       <c r="A16" s="3" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>78</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="17" ht="34" customHeight="1" spans="1:8">
       <c r="A17" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>78</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H17" s="7" t="s">
         <v>125</v>
@@ -5231,51 +5221,51 @@
     </row>
     <row r="18" ht="34" customHeight="1" spans="1:8">
       <c r="A18" s="3" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>78</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="19" ht="34" customHeight="1" spans="1:8">
       <c r="A19" s="3" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>97</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H19" s="7" t="s">
         <v>96</v>
@@ -5283,181 +5273,181 @@
     </row>
     <row r="20" ht="34" customHeight="1" spans="1:8">
       <c r="A20" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>97</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="21" ht="34" customHeight="1" spans="1:8">
       <c r="A21" s="3" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>97</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="22" ht="34" customHeight="1" spans="1:8">
       <c r="A22" s="3" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>97</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="23" ht="34" customHeight="1" spans="1:8">
       <c r="A23" s="3" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="24" ht="34" customHeight="1" spans="1:8">
       <c r="A24" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="25" ht="34" customHeight="1" spans="1:8">
       <c r="A25" s="3" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="26" ht="34" customHeight="1" spans="1:8">
       <c r="A26" s="3" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>171</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H26" s="7" t="s">
         <v>170</v>
@@ -5465,51 +5455,51 @@
     </row>
     <row r="27" ht="34" customHeight="1" spans="1:8">
       <c r="A27" s="3" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>171</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="28" ht="34" customHeight="1" spans="1:8">
       <c r="A28" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>171</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H28" s="7" t="s">
         <v>180</v>
@@ -5517,25 +5507,25 @@
     </row>
     <row r="29" ht="34" customHeight="1" spans="1:8">
       <c r="A29" s="3" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>88</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>87</v>
@@ -5543,129 +5533,129 @@
     </row>
     <row r="30" ht="34" customHeight="1" spans="1:8">
       <c r="A30" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>88</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="31" ht="34" customHeight="1" spans="1:8">
       <c r="A31" s="3" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B31" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>488</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="H31" s="7" t="s">
         <v>257</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>487</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>488</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>489</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>490</v>
-      </c>
-      <c r="G31" s="9" t="s">
-        <v>491</v>
-      </c>
-      <c r="H31" s="7" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="32" ht="34" customHeight="1" spans="1:8">
       <c r="A32" s="3" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="33" ht="34" customHeight="1" spans="1:8">
       <c r="A33" s="3" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="34" ht="34" customHeight="1" spans="1:8">
       <c r="A34" s="3" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>106</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>108</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H34" s="7" t="s">
         <v>105</v>
@@ -5673,51 +5663,51 @@
     </row>
     <row r="35" ht="34" customHeight="1" spans="1:8">
       <c r="A35" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>219</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="36" ht="34" customHeight="1" spans="1:8">
       <c r="A36" s="3" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>219</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H36" s="7" t="s">
         <v>218</v>
@@ -5725,51 +5715,51 @@
     </row>
     <row r="37" ht="34" customHeight="1" spans="1:8">
       <c r="A37" s="3" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>209</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="38" ht="34" customHeight="1" spans="1:8">
       <c r="A38" s="3" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>209</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="G38" s="10" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H38" s="7" t="s">
         <v>208</v>
@@ -5777,129 +5767,129 @@
     </row>
     <row r="39" ht="34" customHeight="1" spans="1:8">
       <c r="A39" s="3" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>209</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="40" ht="34" customHeight="1" spans="1:8">
       <c r="A40" s="3" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="41" ht="34" customHeight="1" spans="1:8">
       <c r="A41" s="3" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="42" ht="34" customHeight="1" spans="1:8">
       <c r="A42" s="3" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>190</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="43" ht="34" customHeight="1" spans="1:8">
       <c r="A43" s="3" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>190</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H43" s="7" t="s">
         <v>199</v>
@@ -5907,296 +5897,296 @@
     </row>
     <row r="44" ht="34" customHeight="1" spans="1:8">
       <c r="A44" s="3" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>190</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="45" ht="34" customHeight="1" spans="1:8">
       <c r="A45" s="3" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B45" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>557</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="G45" s="10" t="s">
+        <v>527</v>
+      </c>
+      <c r="H45" s="7" t="s">
         <v>229</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>556</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>557</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>558</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>559</v>
-      </c>
-      <c r="G45" s="10" t="s">
-        <v>526</v>
-      </c>
-      <c r="H45" s="7" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="46" ht="34" customHeight="1" spans="1:8">
       <c r="A46" s="3" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="47" ht="34" customHeight="1" spans="1:8">
       <c r="A47" s="3" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B47" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>567</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="G47" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="H47" s="7" t="s">
         <v>295</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>566</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>567</v>
-      </c>
-      <c r="E47" s="4" t="s">
-        <v>568</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>569</v>
-      </c>
-      <c r="G47" s="8" t="s">
-        <v>418</v>
-      </c>
-      <c r="H47" s="7" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="48" ht="34" customHeight="1" spans="1:8">
       <c r="A48" s="3" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>108</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="49" ht="34" customHeight="1" spans="1:8">
       <c r="A49" s="3" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="50" ht="34" customHeight="1" spans="1:8">
       <c r="A50" s="3" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H50" s="7" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="51" ht="34" customHeight="1" spans="1:8">
       <c r="A51" s="3" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="52" ht="34" customHeight="1" spans="1:8">
       <c r="A52" s="3" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H52" s="7" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="53" ht="34" customHeight="1" spans="1:8">
       <c r="A53" s="3" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="54" ht="34" customHeight="1" spans="1:8">
       <c r="A54" s="3" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B54" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>603</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>605</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="G54" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="H54" s="7" t="s">
         <v>341</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>602</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>603</v>
-      </c>
-      <c r="E54" s="4" t="s">
-        <v>604</v>
-      </c>
-      <c r="F54" s="4" t="s">
-        <v>605</v>
-      </c>
-      <c r="G54" s="9" t="s">
-        <v>491</v>
-      </c>
-      <c r="H54" s="7" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="11" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B56" s="12" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C56" s="12">
         <v>51</v>
@@ -6205,7 +6195,7 @@
     <row r="57" spans="1:8">
       <c r="A57" s="13"/>
       <c r="B57" s="13" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C57" s="13">
         <v>33</v>
@@ -6214,7 +6204,7 @@
     <row r="58" spans="1:8">
       <c r="A58" s="13"/>
       <c r="B58" s="13" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C58" s="13">
         <v>12</v>
@@ -6223,7 +6213,7 @@
     <row r="59" spans="1:8">
       <c r="A59" s="13"/>
       <c r="B59" s="13" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C59" s="13">
         <v>4</v>
@@ -6232,7 +6222,7 @@
     <row r="60" spans="1:8">
       <c r="A60" s="13"/>
       <c r="B60" s="13" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C60" s="13">
         <v>2</v>
@@ -6241,7 +6231,7 @@
     <row r="61" spans="1:8">
       <c r="A61" s="13"/>
       <c r="B61" s="13" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C61" s="14">
         <v>0.725490196078431</v>

--- a/DevKit_回归测试报告.xlsx
+++ b/DevKit_回归测试报告.xlsx
@@ -4130,8 +4130,8 @@
       <c r="J16" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="K16" s="8" t="s">
-        <v>18</v>
+      <c r="K16" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="L16" s="4" t="s">
         <v>188</v>
@@ -4402,8 +4402,8 @@
       <c r="J23" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="K23" s="8" t="s">
-        <v>18</v>
+      <c r="K23" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="L23" s="4" t="s">
         <v>256</v>

--- a/DevKit_回归测试报告.xlsx
+++ b/DevKit_回归测试报告.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="610">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="861" uniqueCount="611">
   <si>
     <t>DevKit 回归测试 · 结论汇总</t>
   </si>
@@ -885,6 +885,9 @@
   </si>
   <si>
     <t>WsServerTransport.cs:177-180 GetClientKey 仍以 IP:Port 作唯一键，同 NAT 出口同源端口的并发会话会互相覆盖，注释已说明是 HttpSessionClient 无 Id 的框架限制。</t>
+  </si>
+  <si>
+    <t>HttpSessionClient（IHttpSessionClient）没有 Id 属性，用 “IP:Port” 代替。</t>
   </si>
   <si>
     <t>BUG-022</t>
@@ -4446,10 +4449,13 @@
       <c r="L24" s="4" t="s">
         <v>266</v>
       </c>
+      <c r="M24" s="17" t="s">
+        <v>267</v>
+      </c>
     </row>
     <row r="25" ht="92" customHeight="1" spans="1:13">
       <c r="A25" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>78</v>
@@ -4458,36 +4464,36 @@
         <v>45</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K25" s="8" t="s">
         <v>18</v>
       </c>
       <c r="L25" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="26" ht="92" customHeight="1" spans="1:13">
       <c r="A26" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>258</v>
@@ -4496,297 +4502,297 @@
         <v>47</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K26" s="8" t="s">
         <v>18</v>
       </c>
       <c r="L26" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="27" ht="92" customHeight="1" spans="1:13">
       <c r="A27" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C27" s="19" t="s">
         <v>47</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K27" s="6" t="s">
         <v>11</v>
       </c>
       <c r="L27" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="28" ht="92" customHeight="1" spans="1:13">
       <c r="A28" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C28" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K28" s="8" t="s">
         <v>18</v>
       </c>
       <c r="L28" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="29" ht="92" customHeight="1" spans="1:13">
       <c r="A29" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C29" s="18" t="s">
         <v>45</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K29" s="9" t="s">
         <v>37</v>
       </c>
       <c r="L29" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="30" ht="92" customHeight="1" spans="1:13">
       <c r="A30" s="3" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C30" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K30" s="9" t="s">
         <v>37</v>
       </c>
       <c r="L30" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="31" ht="92" customHeight="1" spans="1:13">
       <c r="A31" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C31" s="19" t="s">
         <v>47</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K31" s="9" t="s">
         <v>37</v>
       </c>
       <c r="L31" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="32" ht="92" customHeight="1" spans="1:13">
       <c r="A32" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C32" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K32" s="9" t="s">
         <v>37</v>
       </c>
       <c r="L32" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="33" ht="92" customHeight="1" spans="1:12">
       <c r="A33" s="3" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C33" s="19" t="s">
         <v>47</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K33" s="9" t="s">
         <v>37</v>
       </c>
       <c r="L33" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>
@@ -4826,18 +4832,18 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:8">
       <c r="A3" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>57</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>60</v>
@@ -4846,36 +4852,36 @@
         <v>62</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:8">
       <c r="A4" s="3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>68</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>67</v>
@@ -4883,25 +4889,25 @@
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:8">
       <c r="A5" s="3" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>68</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>67</v>
@@ -4909,25 +4915,25 @@
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:8">
       <c r="A6" s="3" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>68</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>152</v>
@@ -4935,129 +4941,129 @@
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:8">
       <c r="A7" s="3" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>68</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:8">
       <c r="A8" s="3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>68</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:8">
       <c r="A9" s="3" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>68</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:8">
       <c r="A10" s="3" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>135</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1" spans="1:8">
       <c r="A11" s="3" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>135</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>134</v>
@@ -5065,51 +5071,51 @@
     </row>
     <row r="12" ht="34" customHeight="1" spans="1:8">
       <c r="A12" s="3" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>135</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1" spans="1:8">
       <c r="A13" s="3" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>78</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>77</v>
@@ -5117,103 +5123,103 @@
     </row>
     <row r="14" ht="34" customHeight="1" spans="1:8">
       <c r="A14" s="3" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>78</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1" spans="1:8">
       <c r="A15" s="3" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>78</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="16" ht="34" customHeight="1" spans="1:8">
       <c r="A16" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>78</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="17" ht="34" customHeight="1" spans="1:8">
       <c r="A17" s="3" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>78</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H17" s="7" t="s">
         <v>125</v>
@@ -5221,51 +5227,51 @@
     </row>
     <row r="18" ht="34" customHeight="1" spans="1:8">
       <c r="A18" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>78</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="19" ht="34" customHeight="1" spans="1:8">
       <c r="A19" s="3" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>97</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H19" s="7" t="s">
         <v>96</v>
@@ -5273,51 +5279,51 @@
     </row>
     <row r="20" ht="34" customHeight="1" spans="1:8">
       <c r="A20" s="3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>97</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="21" ht="34" customHeight="1" spans="1:8">
       <c r="A21" s="3" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>97</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H21" s="7" t="s">
         <v>248</v>
@@ -5325,129 +5331,129 @@
     </row>
     <row r="22" ht="34" customHeight="1" spans="1:8">
       <c r="A22" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>97</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="23" ht="34" customHeight="1" spans="1:8">
       <c r="A23" s="3" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="24" ht="34" customHeight="1" spans="1:8">
       <c r="A24" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="25" ht="34" customHeight="1" spans="1:8">
       <c r="A25" s="3" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="26" ht="34" customHeight="1" spans="1:8">
       <c r="A26" s="3" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>171</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H26" s="7" t="s">
         <v>170</v>
@@ -5455,51 +5461,51 @@
     </row>
     <row r="27" ht="34" customHeight="1" spans="1:8">
       <c r="A27" s="3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>171</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="28" ht="34" customHeight="1" spans="1:8">
       <c r="A28" s="3" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>171</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H28" s="7" t="s">
         <v>180</v>
@@ -5507,25 +5513,25 @@
     </row>
     <row r="29" ht="34" customHeight="1" spans="1:8">
       <c r="A29" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>88</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>87</v>
@@ -5533,51 +5539,51 @@
     </row>
     <row r="30" ht="34" customHeight="1" spans="1:8">
       <c r="A30" s="3" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>88</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="31" ht="34" customHeight="1" spans="1:8">
       <c r="A31" s="3" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>258</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H31" s="7" t="s">
         <v>257</v>
@@ -5585,77 +5591,77 @@
     </row>
     <row r="32" ht="34" customHeight="1" spans="1:8">
       <c r="A32" s="3" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>258</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="33" ht="34" customHeight="1" spans="1:8">
       <c r="A33" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>258</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="34" ht="34" customHeight="1" spans="1:8">
       <c r="A34" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>106</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>108</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H34" s="7" t="s">
         <v>105</v>
@@ -5663,51 +5669,51 @@
     </row>
     <row r="35" ht="34" customHeight="1" spans="1:8">
       <c r="A35" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>219</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="36" ht="34" customHeight="1" spans="1:8">
       <c r="A36" s="3" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>219</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H36" s="7" t="s">
         <v>218</v>
@@ -5715,51 +5721,51 @@
     </row>
     <row r="37" ht="34" customHeight="1" spans="1:8">
       <c r="A37" s="3" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>209</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="38" ht="34" customHeight="1" spans="1:8">
       <c r="A38" s="3" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>209</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="G38" s="10" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H38" s="7" t="s">
         <v>208</v>
@@ -5767,129 +5773,129 @@
     </row>
     <row r="39" ht="34" customHeight="1" spans="1:8">
       <c r="A39" s="3" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>209</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="40" ht="34" customHeight="1" spans="1:8">
       <c r="A40" s="3" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="41" ht="34" customHeight="1" spans="1:8">
       <c r="A41" s="3" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="42" ht="34" customHeight="1" spans="1:8">
       <c r="A42" s="3" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>190</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="43" ht="34" customHeight="1" spans="1:8">
       <c r="A43" s="3" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>190</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H43" s="7" t="s">
         <v>199</v>
@@ -5897,51 +5903,51 @@
     </row>
     <row r="44" ht="34" customHeight="1" spans="1:8">
       <c r="A44" s="3" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>190</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="45" ht="34" customHeight="1" spans="1:8">
       <c r="A45" s="3" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>230</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H45" s="7" t="s">
         <v>229</v>
@@ -5949,77 +5955,77 @@
     </row>
     <row r="46" ht="34" customHeight="1" spans="1:8">
       <c r="A46" s="3" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>230</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="47" ht="34" customHeight="1" spans="1:8">
       <c r="A47" s="3" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B47" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>568</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>571</v>
+      </c>
+      <c r="G47" s="8" t="s">
+        <v>420</v>
+      </c>
+      <c r="H47" s="7" t="s">
         <v>296</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>567</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>568</v>
-      </c>
-      <c r="E47" s="4" t="s">
-        <v>569</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>570</v>
-      </c>
-      <c r="G47" s="8" t="s">
-        <v>419</v>
-      </c>
-      <c r="H47" s="7" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="48" ht="34" customHeight="1" spans="1:8">
       <c r="A48" s="3" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>240</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>108</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H48" s="7" t="s">
         <v>239</v>
@@ -6027,166 +6033,166 @@
     </row>
     <row r="49" ht="34" customHeight="1" spans="1:8">
       <c r="A49" s="3" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>258</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="50" ht="34" customHeight="1" spans="1:8">
       <c r="A50" s="3" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H50" s="7" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="51" ht="34" customHeight="1" spans="1:8">
       <c r="A51" s="3" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" ht="34" customHeight="1" spans="1:8">
       <c r="A52" s="3" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H52" s="7" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="53" ht="34" customHeight="1" spans="1:8">
       <c r="A53" s="3" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="54" ht="34" customHeight="1" spans="1:8">
       <c r="A54" s="3" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B54" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>604</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>605</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>607</v>
+      </c>
+      <c r="G54" s="9" t="s">
+        <v>493</v>
+      </c>
+      <c r="H54" s="7" t="s">
         <v>342</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>603</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>604</v>
-      </c>
-      <c r="E54" s="4" t="s">
-        <v>605</v>
-      </c>
-      <c r="F54" s="4" t="s">
-        <v>606</v>
-      </c>
-      <c r="G54" s="9" t="s">
-        <v>492</v>
-      </c>
-      <c r="H54" s="7" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="11" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B56" s="12" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C56" s="12">
         <v>51</v>
@@ -6195,7 +6201,7 @@
     <row r="57" spans="1:8">
       <c r="A57" s="13"/>
       <c r="B57" s="13" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C57" s="13">
         <v>33</v>
@@ -6204,7 +6210,7 @@
     <row r="58" spans="1:8">
       <c r="A58" s="13"/>
       <c r="B58" s="13" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C58" s="13">
         <v>12</v>
@@ -6213,7 +6219,7 @@
     <row r="59" spans="1:8">
       <c r="A59" s="13"/>
       <c r="B59" s="13" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C59" s="13">
         <v>4</v>
@@ -6222,7 +6228,7 @@
     <row r="60" spans="1:8">
       <c r="A60" s="13"/>
       <c r="B60" s="13" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C60" s="13">
         <v>2</v>
@@ -6231,7 +6237,7 @@
     <row r="61" spans="1:8">
       <c r="A61" s="13"/>
       <c r="B61" s="13" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C61" s="14">
         <v>0.725490196078431</v>

--- a/DevKit_回归测试报告.xlsx
+++ b/DevKit_回归测试报告.xlsx
@@ -4484,8 +4484,8 @@
       <c r="J25" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="K25" s="8" t="s">
-        <v>18</v>
+      <c r="K25" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="L25" s="4" t="s">
         <v>276</v>

--- a/DevKit_回归测试报告.xlsx
+++ b/DevKit_回归测试报告.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="861" uniqueCount="611">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="612">
   <si>
     <t>DevKit 回归测试 · 结论汇总</t>
   </si>
@@ -947,6 +947,9 @@
   </si>
   <si>
     <t>WsServerTransport.cs:275-279 new WSDataFrame(payload) 发送后未 Dispose，代码注释已写明「要及时释放」但未落实，长时间高频发送会累积底层缓冲。</t>
+  </si>
+  <si>
+    <t>自动GC回收</t>
   </si>
   <si>
     <t>BUG-024</t>
@@ -2776,7 +2779,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2835,6 +2838,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3264,22 +3270,22 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:13">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="23" t="s">
         <v>3</v>
       </c>
     </row>
@@ -3305,175 +3311,175 @@
       <c r="H6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="I6" s="23"/>
-      <c r="J6" s="23"/>
-      <c r="K6" s="23"/>
+      <c r="I6" s="24"/>
+      <c r="J6" s="24"/>
+      <c r="K6" s="24"/>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:13">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="25">
+      <c r="B7" s="26">
         <v>7</v>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="27">
         <v>0.233333333333333</v>
       </c>
-      <c r="D7" s="27" t="s">
+      <c r="D7" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="27" t="s">
+      <c r="E7" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="25" t="s">
+      <c r="F7" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="H7" s="28" t="s">
+      <c r="H7" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="29" t="s">
+      <c r="I7" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="29"/>
-      <c r="K7" s="29" t="s">
+      <c r="J7" s="30"/>
+      <c r="K7" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="L7" s="29"/>
-      <c r="M7" s="29"/>
+      <c r="L7" s="30"/>
+      <c r="M7" s="30"/>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:13">
-      <c r="A8" s="30" t="s">
+      <c r="A8" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="25">
+      <c r="B8" s="26">
         <v>11</v>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="27">
         <v>0.366666666666667</v>
       </c>
-      <c r="D8" s="27" t="s">
+      <c r="D8" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="27" t="s">
+      <c r="E8" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="25" t="s">
+      <c r="F8" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="H8" s="28" t="s">
+      <c r="H8" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="I8" s="29" t="s">
+      <c r="I8" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="J8" s="29"/>
-      <c r="K8" s="29" t="s">
+      <c r="J8" s="30"/>
+      <c r="K8" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="L8" s="29"/>
-      <c r="M8" s="29"/>
+      <c r="L8" s="30"/>
+      <c r="M8" s="30"/>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:13">
-      <c r="A9" s="31" t="s">
+      <c r="A9" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="25">
+      <c r="B9" s="26">
         <v>3</v>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="27">
         <v>0.1</v>
       </c>
-      <c r="D9" s="27" t="s">
+      <c r="D9" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="27" t="s">
+      <c r="E9" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="25" t="s">
+      <c r="F9" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="H9" s="28" t="s">
+      <c r="H9" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="I9" s="29" t="s">
+      <c r="I9" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="J9" s="29"/>
-      <c r="K9" s="29" t="s">
+      <c r="J9" s="30"/>
+      <c r="K9" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="L9" s="29"/>
-      <c r="M9" s="29"/>
+      <c r="L9" s="30"/>
+      <c r="M9" s="30"/>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:13">
-      <c r="A10" s="32" t="s">
+      <c r="A10" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="25">
+      <c r="B10" s="26">
         <v>4</v>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="27">
         <v>0.133333333333333</v>
       </c>
-      <c r="D10" s="27" t="s">
+      <c r="D10" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="27" t="s">
+      <c r="E10" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="25" t="s">
+      <c r="F10" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="H10" s="28" t="s">
+      <c r="H10" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="I10" s="29" t="s">
+      <c r="I10" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="J10" s="29"/>
-      <c r="K10" s="29" t="s">
+      <c r="J10" s="30"/>
+      <c r="K10" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="L10" s="29"/>
-      <c r="M10" s="29"/>
+      <c r="L10" s="30"/>
+      <c r="M10" s="30"/>
     </row>
     <row r="11" spans="1:13">
-      <c r="A11" s="33" t="s">
+      <c r="A11" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="25">
+      <c r="B11" s="26">
         <v>5</v>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="27">
         <v>0.166666666666667</v>
       </c>
-      <c r="D11" s="27" t="s">
+      <c r="D11" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="E11" s="27" t="s">
+      <c r="E11" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="25" t="s">
+      <c r="F11" s="26" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="12" ht="27" spans="1:13">
-      <c r="A12" s="34" t="s">
+      <c r="A12" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="35">
+      <c r="B12" s="36">
         <v>30</v>
       </c>
-      <c r="C12" s="36">
+      <c r="C12" s="37">
         <v>1</v>
       </c>
-      <c r="D12" s="34" t="s">
+      <c r="D12" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="E12" s="34" t="s">
+      <c r="E12" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="F12" s="35" t="s">
+      <c r="F12" s="36" t="s">
         <v>14</v>
       </c>
     </row>
@@ -3481,37 +3487,37 @@
       <c r="H13" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I13" s="23"/>
+      <c r="I13" s="24"/>
     </row>
     <row r="14" spans="1:13">
-      <c r="H14" s="37" t="s">
+      <c r="H14" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="I14" s="38">
+      <c r="I14" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:13">
-      <c r="H15" s="39" t="s">
+      <c r="H15" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="I15" s="38">
+      <c r="I15" s="39">
         <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:13">
-      <c r="H16" s="40" t="s">
+      <c r="H16" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="I16" s="38">
+      <c r="I16" s="39">
         <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="H17" s="41" t="s">
+      <c r="H17" s="42" t="s">
         <v>47</v>
       </c>
-      <c r="I17" s="38">
+      <c r="I17" s="39">
         <v>6</v>
       </c>
     </row>
@@ -3519,40 +3525,40 @@
       <c r="A18" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="H18" s="42" t="s">
+      <c r="H18" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="I18" s="42">
+      <c r="I18" s="43">
         <v>16</v>
       </c>
     </row>
     <row r="19" ht="26" customHeight="1" spans="1:9">
-      <c r="A19" s="43" t="s">
+      <c r="A19" s="44" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="20" ht="26" customHeight="1" spans="1:9">
-      <c r="A20" s="43" t="s">
+      <c r="A20" s="44" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="21" ht="26" customHeight="1" spans="1:9">
-      <c r="A21" s="43" t="s">
+      <c r="A21" s="44" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1" spans="1:9">
-      <c r="A22" s="43" t="s">
+      <c r="A22" s="44" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="23" ht="26" customHeight="1" spans="1:9">
-      <c r="A23" s="43" t="s">
+      <c r="A23" s="44" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="24" ht="26" customHeight="1" spans="1:9">
-      <c r="A24" s="43" t="s">
+      <c r="A24" s="44" t="s">
         <v>54</v>
       </c>
     </row>
@@ -3598,6 +3604,7 @@
     <col min="9" max="10" width="38" customWidth="1"/>
     <col min="11" max="11" width="10" customWidth="1"/>
     <col min="12" max="12" width="56" customWidth="1"/>
+    <col min="13" max="13" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:13">
@@ -4528,271 +4535,274 @@
       <c r="L26" s="4" t="s">
         <v>285</v>
       </c>
+      <c r="M26" s="21" t="s">
+        <v>286</v>
+      </c>
     </row>
     <row r="27" ht="92" customHeight="1" spans="1:13">
       <c r="A27" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C27" s="19" t="s">
         <v>47</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K27" s="6" t="s">
         <v>11</v>
       </c>
       <c r="L27" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="28" ht="92" customHeight="1" spans="1:13">
       <c r="A28" s="3" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C28" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="K28" s="8" t="s">
-        <v>18</v>
+        <v>305</v>
+      </c>
+      <c r="K28" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="L28" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="29" ht="92" customHeight="1" spans="1:13">
       <c r="A29" s="3" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C29" s="18" t="s">
         <v>45</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K29" s="9" t="s">
         <v>37</v>
       </c>
       <c r="L29" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="30" ht="92" customHeight="1" spans="1:13">
       <c r="A30" s="3" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C30" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K30" s="9" t="s">
         <v>37</v>
       </c>
       <c r="L30" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="31" ht="92" customHeight="1" spans="1:13">
       <c r="A31" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C31" s="19" t="s">
         <v>47</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K31" s="9" t="s">
         <v>37</v>
       </c>
       <c r="L31" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="32" ht="92" customHeight="1" spans="1:13">
       <c r="A32" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C32" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K32" s="9" t="s">
         <v>37</v>
       </c>
       <c r="L32" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="33" ht="92" customHeight="1" spans="1:12">
       <c r="A33" s="3" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C33" s="19" t="s">
         <v>47</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K33" s="9" t="s">
         <v>37</v>
       </c>
       <c r="L33" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -4832,18 +4842,18 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:8">
       <c r="A3" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>57</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>60</v>
@@ -4852,36 +4862,36 @@
         <v>62</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:8">
       <c r="A4" s="3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>68</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>67</v>
@@ -4889,25 +4899,25 @@
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:8">
       <c r="A5" s="3" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>68</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>67</v>
@@ -4915,25 +4925,25 @@
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:8">
       <c r="A6" s="3" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>68</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>152</v>
@@ -4941,129 +4951,129 @@
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:8">
       <c r="A7" s="3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>68</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:8">
       <c r="A8" s="3" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>68</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:8">
       <c r="A9" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>68</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:8">
       <c r="A10" s="3" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>135</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="11" ht="34" customHeight="1" spans="1:8">
       <c r="A11" s="3" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>135</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>134</v>
@@ -5071,51 +5081,51 @@
     </row>
     <row r="12" ht="34" customHeight="1" spans="1:8">
       <c r="A12" s="3" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>135</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="13" ht="34" customHeight="1" spans="1:8">
       <c r="A13" s="3" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>78</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>77</v>
@@ -5123,77 +5133,77 @@
     </row>
     <row r="14" ht="34" customHeight="1" spans="1:8">
       <c r="A14" s="3" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>78</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="15" ht="34" customHeight="1" spans="1:8">
       <c r="A15" s="3" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>78</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="16" ht="34" customHeight="1" spans="1:8">
       <c r="A16" s="3" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>78</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H16" s="7" t="s">
         <v>268</v>
@@ -5201,25 +5211,25 @@
     </row>
     <row r="17" ht="34" customHeight="1" spans="1:8">
       <c r="A17" s="3" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>78</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H17" s="7" t="s">
         <v>125</v>
@@ -5227,51 +5237,51 @@
     </row>
     <row r="18" ht="34" customHeight="1" spans="1:8">
       <c r="A18" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>78</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="19" ht="34" customHeight="1" spans="1:8">
       <c r="A19" s="3" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>97</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H19" s="7" t="s">
         <v>96</v>
@@ -5279,51 +5289,51 @@
     </row>
     <row r="20" ht="34" customHeight="1" spans="1:8">
       <c r="A20" s="3" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>97</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="21" ht="34" customHeight="1" spans="1:8">
       <c r="A21" s="3" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>97</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H21" s="7" t="s">
         <v>248</v>
@@ -5331,129 +5341,129 @@
     </row>
     <row r="22" ht="34" customHeight="1" spans="1:8">
       <c r="A22" s="3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>97</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="23" ht="34" customHeight="1" spans="1:8">
       <c r="A23" s="3" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="24" ht="34" customHeight="1" spans="1:8">
       <c r="A24" s="3" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="25" ht="34" customHeight="1" spans="1:8">
       <c r="A25" s="3" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="26" ht="34" customHeight="1" spans="1:8">
       <c r="A26" s="3" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>171</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H26" s="7" t="s">
         <v>170</v>
@@ -5461,51 +5471,51 @@
     </row>
     <row r="27" ht="34" customHeight="1" spans="1:8">
       <c r="A27" s="3" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>171</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="28" ht="34" customHeight="1" spans="1:8">
       <c r="A28" s="3" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>171</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H28" s="7" t="s">
         <v>180</v>
@@ -5513,25 +5523,25 @@
     </row>
     <row r="29" ht="34" customHeight="1" spans="1:8">
       <c r="A29" s="3" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>88</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>87</v>
@@ -5539,51 +5549,51 @@
     </row>
     <row r="30" ht="34" customHeight="1" spans="1:8">
       <c r="A30" s="3" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>88</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="31" ht="34" customHeight="1" spans="1:8">
       <c r="A31" s="3" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>258</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H31" s="7" t="s">
         <v>257</v>
@@ -5591,77 +5601,77 @@
     </row>
     <row r="32" ht="34" customHeight="1" spans="1:8">
       <c r="A32" s="3" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>258</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="33" ht="34" customHeight="1" spans="1:8">
       <c r="A33" s="3" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>258</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="34" ht="34" customHeight="1" spans="1:8">
       <c r="A34" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>106</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>108</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H34" s="7" t="s">
         <v>105</v>
@@ -5669,51 +5679,51 @@
     </row>
     <row r="35" ht="34" customHeight="1" spans="1:8">
       <c r="A35" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>219</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="36" ht="34" customHeight="1" spans="1:8">
       <c r="A36" s="3" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>219</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H36" s="7" t="s">
         <v>218</v>
@@ -5721,51 +5731,51 @@
     </row>
     <row r="37" ht="34" customHeight="1" spans="1:8">
       <c r="A37" s="3" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>209</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="38" ht="34" customHeight="1" spans="1:8">
       <c r="A38" s="3" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>209</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="G38" s="10" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H38" s="7" t="s">
         <v>208</v>
@@ -5773,129 +5783,129 @@
     </row>
     <row r="39" ht="34" customHeight="1" spans="1:8">
       <c r="A39" s="3" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>209</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="40" ht="34" customHeight="1" spans="1:8">
       <c r="A40" s="3" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="41" ht="34" customHeight="1" spans="1:8">
       <c r="A41" s="3" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="42" ht="34" customHeight="1" spans="1:8">
       <c r="A42" s="3" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>190</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="43" ht="34" customHeight="1" spans="1:8">
       <c r="A43" s="3" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>190</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H43" s="7" t="s">
         <v>199</v>
@@ -5903,51 +5913,51 @@
     </row>
     <row r="44" ht="34" customHeight="1" spans="1:8">
       <c r="A44" s="3" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>190</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="45" ht="34" customHeight="1" spans="1:8">
       <c r="A45" s="3" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>230</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H45" s="7" t="s">
         <v>229</v>
@@ -5955,77 +5965,77 @@
     </row>
     <row r="46" ht="34" customHeight="1" spans="1:8">
       <c r="A46" s="3" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>230</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="47" ht="34" customHeight="1" spans="1:8">
       <c r="A47" s="3" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B47" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>571</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>572</v>
+      </c>
+      <c r="G47" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="H47" s="7" t="s">
         <v>297</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>568</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>569</v>
-      </c>
-      <c r="E47" s="4" t="s">
-        <v>570</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="G47" s="8" t="s">
-        <v>420</v>
-      </c>
-      <c r="H47" s="7" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="48" ht="34" customHeight="1" spans="1:8">
       <c r="A48" s="3" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>240</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>108</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H48" s="7" t="s">
         <v>239</v>
@@ -6033,25 +6043,25 @@
     </row>
     <row r="49" ht="34" customHeight="1" spans="1:8">
       <c r="A49" s="3" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>258</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H49" s="7" t="s">
         <v>277</v>
@@ -6059,140 +6069,140 @@
     </row>
     <row r="50" ht="34" customHeight="1" spans="1:8">
       <c r="A50" s="3" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H50" s="7" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="51" ht="34" customHeight="1" spans="1:8">
       <c r="A51" s="3" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" ht="34" customHeight="1" spans="1:8">
       <c r="A52" s="3" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H52" s="7" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="53" ht="34" customHeight="1" spans="1:8">
       <c r="A53" s="3" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="54" ht="34" customHeight="1" spans="1:8">
       <c r="A54" s="3" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B54" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>607</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>608</v>
+      </c>
+      <c r="G54" s="9" t="s">
+        <v>494</v>
+      </c>
+      <c r="H54" s="7" t="s">
         <v>343</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>604</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>605</v>
-      </c>
-      <c r="E54" s="4" t="s">
-        <v>606</v>
-      </c>
-      <c r="F54" s="4" t="s">
-        <v>607</v>
-      </c>
-      <c r="G54" s="9" t="s">
-        <v>493</v>
-      </c>
-      <c r="H54" s="7" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="11" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B56" s="12" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C56" s="12">
         <v>51</v>
@@ -6201,7 +6211,7 @@
     <row r="57" spans="1:8">
       <c r="A57" s="13"/>
       <c r="B57" s="13" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C57" s="13">
         <v>33</v>
@@ -6210,7 +6220,7 @@
     <row r="58" spans="1:8">
       <c r="A58" s="13"/>
       <c r="B58" s="13" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C58" s="13">
         <v>12</v>
@@ -6219,7 +6229,7 @@
     <row r="59" spans="1:8">
       <c r="A59" s="13"/>
       <c r="B59" s="13" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C59" s="13">
         <v>4</v>
@@ -6228,7 +6238,7 @@
     <row r="60" spans="1:8">
       <c r="A60" s="13"/>
       <c r="B60" s="13" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C60" s="13">
         <v>2</v>
@@ -6237,7 +6247,7 @@
     <row r="61" spans="1:8">
       <c r="A61" s="13"/>
       <c r="B61" s="13" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C61" s="14">
         <v>0.725490196078431</v>

--- a/DevKit_回归测试报告.xlsx
+++ b/DevKit_回归测试报告.xlsx
@@ -4646,8 +4646,8 @@
       <c r="J29" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="K29" s="9" t="s">
-        <v>37</v>
+      <c r="K29" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="L29" s="4" t="s">
         <v>316</v>
@@ -4684,8 +4684,8 @@
       <c r="J30" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="K30" s="9" t="s">
-        <v>37</v>
+      <c r="K30" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="L30" s="4" t="s">
         <v>316</v>

--- a/DevKit_回归测试报告.xlsx
+++ b/DevKit_回归测试报告.xlsx
@@ -4722,8 +4722,8 @@
       <c r="J31" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="K31" s="9" t="s">
-        <v>37</v>
+      <c r="K31" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="L31" s="4" t="s">
         <v>316</v>

--- a/DevKit_回归测试报告.xlsx
+++ b/DevKit_回归测试报告.xlsx
@@ -4760,8 +4760,8 @@
       <c r="J32" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="K32" s="9" t="s">
-        <v>37</v>
+      <c r="K32" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="L32" s="4" t="s">
         <v>316</v>

--- a/DevKit_回归测试报告.xlsx
+++ b/DevKit_回归测试报告.xlsx
@@ -4798,8 +4798,8 @@
       <c r="J33" s="4" t="s">
         <v>351</v>
       </c>
-      <c r="K33" s="9" t="s">
-        <v>37</v>
+      <c r="K33" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="L33" s="4" t="s">
         <v>316</v>
